--- a/medical_surveys_questionnaires/005_cardiomessenger_order_form--medical_surveys_questionnaires.xlsx
+++ b/medical_surveys_questionnaires/005_cardiomessenger_order_form--medical_surveys_questionnaires.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -896,8 +896,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -925,12 +925,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'cardiomessenger_smart_(mobile)',_'value':_'smart'}</t>
+          <t>cardiomessenger_smart_(mobile)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'CardioMessenger Smart (Mobile)', 'value': 'smart'}</t>
+          <t>CardioMessenger Smart (Mobile)</t>
         </is>
       </c>
     </row>
@@ -942,12 +942,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'cardiomessenger_ii_(bedside)',_'value':_'bedside'}</t>
+          <t>cardiomessenger_ii_(bedside)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'CardioMessenger II (Bedside)', 'value': 'bedside'}</t>
+          <t>CardioMessenger II (Bedside)</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'cardiomessenger_pro_(advanced)',_'value':_'pro'}</t>
+          <t>cardiomessenger_pro_(advanced)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'CardioMessenger Pro (Advanced)', 'value': 'pro'}</t>
+          <t>CardioMessenger Pro (Advanced)</t>
         </is>
       </c>
     </row>
@@ -976,12 +976,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'standard_ground_(5-7_days)',_'value':_'ground'}</t>
+          <t>standard_ground_(5-7_days)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Standard Ground (5-7 days)', 'value': 'ground'}</t>
+          <t>Standard Ground (5-7 days)</t>
         </is>
       </c>
     </row>
@@ -993,12 +993,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'expedited_(2-3_days)',_'value':_'expedited'}</t>
+          <t>expedited_(2-3_days)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Expedited (2-3 days)', 'value': 'expedited'}</t>
+          <t>Expedited (2-3 days)</t>
         </is>
       </c>
     </row>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'overnight_priority',_'value':_'overnight'}</t>
+          <t>overnight_priority</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Overnight Priority', 'value': 'overnight'}</t>
+          <t>Overnight Priority</t>
         </is>
       </c>
     </row>
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'authorized_and_confirmed',_'value':_'authorized'}</t>
+          <t>authorized_and_confirmed</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Authorized and Confirmed', 'value': 'authorized'}</t>
+          <t>Authorized and Confirmed</t>
         </is>
       </c>
     </row>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'not_authorized',_'value':_'not_authorized'}</t>
+          <t>not_authorized</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Not Authorized', 'value': 'not_authorized'}</t>
+          <t>Not Authorized</t>
         </is>
       </c>
     </row>
